--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L688"/>
+  <dimension ref="A1:L690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29344,6 +29344,90 @@
       <c r="L688" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:27+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="C689" t="n">
+        <v>349.37</v>
+      </c>
+      <c r="D689" t="n">
+        <v>352.56</v>
+      </c>
+      <c r="E689" t="n">
+        <v>356.13</v>
+      </c>
+      <c r="F689" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="G689" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="H689" t="n">
+        <v>361.95</v>
+      </c>
+      <c r="I689" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="J689" t="n">
+        <v>358.03</v>
+      </c>
+      <c r="K689" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>360.54</v>
+      </c>
+      <c r="C690" t="n">
+        <v>349.97</v>
+      </c>
+      <c r="D690" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="E690" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="F690" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="G690" t="n">
+        <v>358.85</v>
+      </c>
+      <c r="H690" t="n">
+        <v>361.98</v>
+      </c>
+      <c r="I690" t="n">
+        <v>356.88</v>
+      </c>
+      <c r="J690" t="n">
+        <v>358.03</v>
+      </c>
+      <c r="K690" t="n">
+        <v>348.88</v>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29358,7 +29442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B723"/>
+  <dimension ref="A1:B725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36591,6 +36675,26 @@
       </c>
       <c r="B723" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -36759,28 +36863,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5700769614916156</v>
+        <v>-0.5676860886982638</v>
       </c>
       <c r="J2" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K2" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2736384129507921</v>
+        <v>0.2730311116092159</v>
       </c>
       <c r="M2" t="n">
-        <v>5.579816685858884</v>
+        <v>5.574130719429253</v>
       </c>
       <c r="N2" t="n">
-        <v>49.98725656242565</v>
+        <v>49.8940565615497</v>
       </c>
       <c r="O2" t="n">
-        <v>7.070166657330338</v>
+        <v>7.063572506993165</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5291651962772</v>
+        <v>371.5040713046409</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36837,28 +36941,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5248476626118423</v>
+        <v>-0.5209530697081762</v>
       </c>
       <c r="J3" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K3" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2009611813276294</v>
+        <v>0.199251111857964</v>
       </c>
       <c r="M3" t="n">
-        <v>6.492741571741124</v>
+        <v>6.494787115129822</v>
       </c>
       <c r="N3" t="n">
-        <v>63.46565319269973</v>
+        <v>63.41929607369225</v>
       </c>
       <c r="O3" t="n">
-        <v>7.96653332339103</v>
+        <v>7.963623300589516</v>
       </c>
       <c r="P3" t="n">
-        <v>356.8834082845514</v>
+        <v>356.8425314918572</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36915,28 +37019,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3934578924166787</v>
+        <v>-0.3873645663814091</v>
       </c>
       <c r="J4" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K4" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1339094328552858</v>
+        <v>0.1303963003071029</v>
       </c>
       <c r="M4" t="n">
-        <v>6.003880245095612</v>
+        <v>6.013521158725921</v>
       </c>
       <c r="N4" t="n">
-        <v>58.0183236340639</v>
+        <v>58.18680571072342</v>
       </c>
       <c r="O4" t="n">
-        <v>7.616976016377096</v>
+        <v>7.628027642236453</v>
       </c>
       <c r="P4" t="n">
-        <v>352.2129683056093</v>
+        <v>352.1490157658397</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36993,28 +37097,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2992117032407156</v>
+        <v>-0.2921381444188402</v>
       </c>
       <c r="J5" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K5" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07203855674619564</v>
+        <v>0.06887881477123081</v>
       </c>
       <c r="M5" t="n">
-        <v>6.40731219763666</v>
+        <v>6.420230429989083</v>
       </c>
       <c r="N5" t="n">
-        <v>66.82494296140668</v>
+        <v>67.08504245866449</v>
       </c>
       <c r="O5" t="n">
-        <v>8.17465246731668</v>
+        <v>8.190545919452774</v>
       </c>
       <c r="P5" t="n">
-        <v>351.8445279268542</v>
+        <v>351.7702863296561</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37071,28 +37175,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2866055124856304</v>
+        <v>-0.28007514721264</v>
       </c>
       <c r="J6" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K6" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05452396481184341</v>
+        <v>0.05227983101590583</v>
       </c>
       <c r="M6" t="n">
-        <v>7.433054107801258</v>
+        <v>7.43842042552699</v>
       </c>
       <c r="N6" t="n">
-        <v>82.53700215426674</v>
+        <v>82.68442630371584</v>
       </c>
       <c r="O6" t="n">
-        <v>9.084987735504475</v>
+        <v>9.093097728701471</v>
       </c>
       <c r="P6" t="n">
-        <v>351.7967269944252</v>
+        <v>351.728187665293</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37149,28 +37253,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2956973041328465</v>
+        <v>-0.2891179184138145</v>
       </c>
       <c r="J7" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K7" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06231709538743568</v>
+        <v>0.05980789478099757</v>
       </c>
       <c r="M7" t="n">
-        <v>7.045975204256022</v>
+        <v>7.054812646996185</v>
       </c>
       <c r="N7" t="n">
-        <v>76.23598950313531</v>
+        <v>76.40762926020017</v>
       </c>
       <c r="O7" t="n">
-        <v>8.731322322714659</v>
+        <v>8.741145763582722</v>
       </c>
       <c r="P7" t="n">
-        <v>355.3827612672646</v>
+        <v>355.3137076428284</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37227,28 +37331,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2938065241193754</v>
+        <v>-0.2869233095013722</v>
       </c>
       <c r="J8" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K8" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06373406819518801</v>
+        <v>0.06099354730591955</v>
       </c>
       <c r="M8" t="n">
-        <v>6.846606625018135</v>
+        <v>6.861011289223374</v>
       </c>
       <c r="N8" t="n">
-        <v>73.4796309622209</v>
+        <v>73.69617901158722</v>
       </c>
       <c r="O8" t="n">
-        <v>8.572026071018502</v>
+        <v>8.584647867652302</v>
       </c>
       <c r="P8" t="n">
-        <v>357.6480343064176</v>
+        <v>357.5757910611683</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37305,28 +37409,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3381099180978995</v>
+        <v>-0.3312636094489491</v>
       </c>
       <c r="J9" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K9" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08793672230441529</v>
+        <v>0.08472570252035649</v>
       </c>
       <c r="M9" t="n">
-        <v>6.860428409988821</v>
+        <v>6.873423038652406</v>
       </c>
       <c r="N9" t="n">
-        <v>68.70479260190692</v>
+        <v>68.93061781221698</v>
       </c>
       <c r="O9" t="n">
-        <v>8.288835418917841</v>
+        <v>8.302446495594957</v>
       </c>
       <c r="P9" t="n">
-        <v>353.8891707659232</v>
+        <v>353.8173150873627</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37383,28 +37487,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4901351069384349</v>
+        <v>-0.481066159154536</v>
       </c>
       <c r="J10" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K10" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2333832908635221</v>
+        <v>0.2250454035282488</v>
       </c>
       <c r="M10" t="n">
-        <v>5.402385209313714</v>
+        <v>5.432706556908417</v>
       </c>
       <c r="N10" t="n">
-        <v>45.7253100488532</v>
+        <v>46.338753760694</v>
       </c>
       <c r="O10" t="n">
-        <v>6.762049249218258</v>
+        <v>6.807257433114602</v>
       </c>
       <c r="P10" t="n">
-        <v>355.1175689194116</v>
+        <v>355.0223852199946</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37461,28 +37565,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5447174585218069</v>
+        <v>-0.5409669639709068</v>
       </c>
       <c r="J11" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="K11" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3376604353719832</v>
+        <v>0.3351563233443909</v>
       </c>
       <c r="M11" t="n">
-        <v>4.71082080421463</v>
+        <v>4.716972344579726</v>
       </c>
       <c r="N11" t="n">
-        <v>33.72559556663828</v>
+        <v>33.75532058140557</v>
       </c>
       <c r="O11" t="n">
-        <v>5.807374240277466</v>
+        <v>5.80993292400227</v>
       </c>
       <c r="P11" t="n">
-        <v>356.8415741470631</v>
+        <v>356.8022104509805</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37520,7 +37624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L688"/>
+  <dimension ref="A1:L690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80179,6 +80283,130 @@
         </is>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:27+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-43.46590031943039,169.75882713374014</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-43.465421733451464,169.7594466552836</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-43.464868583246414,169.7599247329378</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-43.46430973642655,169.76038823650956</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-43.463764088253654,169.7608776047345</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-43.4632009494314,169.76132686323754</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>-43.46264157496983,169.76173789022684</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>-43.4620576988689,169.76209193044357</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>-43.46144018180407,169.76236988503794</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>-43.46084598232143,169.7627444799112</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-43.46589910058116,169.75882483791833</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-43.465418553868524,169.7594406662037</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-43.464869843739514,169.75992713981998</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-43.464307475158755,169.76038377572354</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-43.46376596544239,169.7608813788471</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-43.46320344981753,169.7613321450084</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>-43.46264145433092,169.76173755875917</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>-43.46205811623533,169.76209343039503</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>-43.46144018180407,169.76236988503794</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>-43.46084569248263,169.76274331065585</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L690"/>
+  <dimension ref="A1:L694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29420,7 +29420,7 @@
         <v>356.88</v>
       </c>
       <c r="J690" t="n">
-        <v>358.03</v>
+        <v>357.37</v>
       </c>
       <c r="K690" t="n">
         <v>348.88</v>
@@ -29428,6 +29428,174 @@
       <c r="L690" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:19:37+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>360.96</v>
+      </c>
+      <c r="C691" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="D691" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="E691" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="F691" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="G691" t="n">
+        <v>358.44</v>
+      </c>
+      <c r="H691" t="n">
+        <v>361.82</v>
+      </c>
+      <c r="I691" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="J691" t="n">
+        <v>357.27</v>
+      </c>
+      <c r="K691" t="n">
+        <v>347.27</v>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:25:50+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>362.45</v>
+      </c>
+      <c r="C692" t="n">
+        <v>352</v>
+      </c>
+      <c r="D692" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="E692" t="n">
+        <v>357.29</v>
+      </c>
+      <c r="F692" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="G692" t="n">
+        <v>359.18</v>
+      </c>
+      <c r="H692" t="n">
+        <v>362.38</v>
+      </c>
+      <c r="I692" t="n">
+        <v>357.37</v>
+      </c>
+      <c r="J692" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="K692" t="n">
+        <v>346.97</v>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:25:58+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>362.64</v>
+      </c>
+      <c r="C693" t="n">
+        <v>352.44</v>
+      </c>
+      <c r="D693" t="n">
+        <v>353.43</v>
+      </c>
+      <c r="E693" t="n">
+        <v>357.78</v>
+      </c>
+      <c r="F693" t="n">
+        <v>357.23</v>
+      </c>
+      <c r="G693" t="n">
+        <v>358.65</v>
+      </c>
+      <c r="H693" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="I693" t="n">
+        <v>356.32</v>
+      </c>
+      <c r="J693" t="n">
+        <v>355.95</v>
+      </c>
+      <c r="K693" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>362.81</v>
+      </c>
+      <c r="C694" t="n">
+        <v>352.87</v>
+      </c>
+      <c r="D694" t="n">
+        <v>353.83</v>
+      </c>
+      <c r="E694" t="n">
+        <v>358.27</v>
+      </c>
+      <c r="F694" t="n">
+        <v>357.65</v>
+      </c>
+      <c r="G694" t="n">
+        <v>358.33</v>
+      </c>
+      <c r="H694" t="n">
+        <v>360.97</v>
+      </c>
+      <c r="I694" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="J694" t="n">
+        <v>354.87</v>
+      </c>
+      <c r="K694" t="n">
+        <v>347.16</v>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29442,7 +29610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B725"/>
+  <dimension ref="A1:B730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36695,6 +36863,56 @@
       </c>
       <c r="B725" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>1.02</v>
       </c>
     </row>
   </sheetData>
@@ -36863,28 +37081,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5676860886982638</v>
+        <v>-0.5609820514873879</v>
       </c>
       <c r="J2" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K2" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2730311116092159</v>
+        <v>0.2700061116535737</v>
       </c>
       <c r="M2" t="n">
-        <v>5.574130719429253</v>
+        <v>5.571092359118984</v>
       </c>
       <c r="N2" t="n">
-        <v>49.8940565615497</v>
+        <v>49.8154578656691</v>
       </c>
       <c r="O2" t="n">
-        <v>7.063572506993165</v>
+        <v>7.058006649590881</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5040713046409</v>
+        <v>371.4335229744342</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36941,28 +37159,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5209530697081762</v>
+        <v>-0.5108538757731814</v>
       </c>
       <c r="J3" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K3" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L3" t="n">
-        <v>0.199251111857964</v>
+        <v>0.1938873349976354</v>
       </c>
       <c r="M3" t="n">
-        <v>6.494787115129822</v>
+        <v>6.51142049232587</v>
       </c>
       <c r="N3" t="n">
-        <v>63.41929607369225</v>
+        <v>63.52727881984223</v>
       </c>
       <c r="O3" t="n">
-        <v>7.963623300589516</v>
+        <v>7.970400166857511</v>
       </c>
       <c r="P3" t="n">
-        <v>356.8425314918572</v>
+        <v>356.736255485636</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37019,28 +37237,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3873645663814091</v>
+        <v>-0.3748241911863279</v>
       </c>
       <c r="J4" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K4" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1303963003071029</v>
+        <v>0.1231373622807498</v>
       </c>
       <c r="M4" t="n">
-        <v>6.013521158725921</v>
+        <v>6.037061104265709</v>
       </c>
       <c r="N4" t="n">
-        <v>58.18680571072342</v>
+        <v>58.57570286900098</v>
       </c>
       <c r="O4" t="n">
-        <v>7.628027642236453</v>
+        <v>7.65347652175147</v>
       </c>
       <c r="P4" t="n">
-        <v>352.1490157658397</v>
+        <v>352.0170550784688</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37097,28 +37315,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2921381444188402</v>
+        <v>-0.2771289682466977</v>
       </c>
       <c r="J5" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K5" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06887881477123081</v>
+        <v>0.06225274096955968</v>
       </c>
       <c r="M5" t="n">
-        <v>6.420230429989083</v>
+        <v>6.451200659864848</v>
       </c>
       <c r="N5" t="n">
-        <v>67.08504245866449</v>
+        <v>67.73478231170694</v>
       </c>
       <c r="O5" t="n">
-        <v>8.190545919452774</v>
+        <v>8.230114355931327</v>
       </c>
       <c r="P5" t="n">
-        <v>351.7702863296561</v>
+        <v>351.6123480781402</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37175,28 +37393,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.28007514721264</v>
+        <v>-0.2661085033796872</v>
       </c>
       <c r="J6" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K6" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05227983101590583</v>
+        <v>0.04751842005635454</v>
       </c>
       <c r="M6" t="n">
-        <v>7.43842042552699</v>
+        <v>7.453294858578125</v>
       </c>
       <c r="N6" t="n">
-        <v>82.68442630371584</v>
+        <v>83.10605411573476</v>
       </c>
       <c r="O6" t="n">
-        <v>9.093097728701471</v>
+        <v>9.116252196804055</v>
       </c>
       <c r="P6" t="n">
-        <v>351.728187665293</v>
+        <v>351.5812186535825</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37253,28 +37471,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2891179184138145</v>
+        <v>-0.276742667557932</v>
       </c>
       <c r="J7" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K7" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05980789478099757</v>
+        <v>0.05525383097355341</v>
       </c>
       <c r="M7" t="n">
-        <v>7.054812646996185</v>
+        <v>7.069020548641264</v>
       </c>
       <c r="N7" t="n">
-        <v>76.40762926020017</v>
+        <v>76.67001613327801</v>
       </c>
       <c r="O7" t="n">
-        <v>8.741145763582722</v>
+        <v>8.756141623642117</v>
       </c>
       <c r="P7" t="n">
-        <v>355.3137076428284</v>
+        <v>355.1834916305806</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37331,28 +37549,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2869233095013722</v>
+        <v>-0.2736533168600668</v>
       </c>
       <c r="J8" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K8" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06099354730591955</v>
+        <v>0.05587869422478065</v>
       </c>
       <c r="M8" t="n">
-        <v>6.861011289223374</v>
+        <v>6.888626551561914</v>
       </c>
       <c r="N8" t="n">
-        <v>73.69617901158722</v>
+        <v>74.0804388733516</v>
       </c>
       <c r="O8" t="n">
-        <v>8.584647867652302</v>
+        <v>8.606999411720183</v>
       </c>
       <c r="P8" t="n">
-        <v>357.5757910611683</v>
+        <v>357.436162044028</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37409,28 +37627,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3312636094489491</v>
+        <v>-0.318248919119416</v>
       </c>
       <c r="J9" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K9" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08472570252035649</v>
+        <v>0.07881228502716109</v>
       </c>
       <c r="M9" t="n">
-        <v>6.873423038652406</v>
+        <v>6.897047195723663</v>
       </c>
       <c r="N9" t="n">
-        <v>68.93061781221698</v>
+        <v>69.31203615049857</v>
       </c>
       <c r="O9" t="n">
-        <v>8.302446495594957</v>
+        <v>8.325385045179507</v>
       </c>
       <c r="P9" t="n">
-        <v>353.8173150873627</v>
+        <v>353.6803740224377</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37487,28 +37705,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.481066159154536</v>
+        <v>-0.465457750455376</v>
       </c>
       <c r="J10" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K10" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2250454035282488</v>
+        <v>0.2118493923962129</v>
       </c>
       <c r="M10" t="n">
-        <v>5.432706556908417</v>
+        <v>5.48140954760987</v>
       </c>
       <c r="N10" t="n">
-        <v>46.338753760694</v>
+        <v>47.19142468872106</v>
       </c>
       <c r="O10" t="n">
-        <v>6.807257433114602</v>
+        <v>6.869601494171336</v>
       </c>
       <c r="P10" t="n">
-        <v>355.0223852199946</v>
+        <v>354.8581520084099</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37565,28 +37783,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5409669639709068</v>
+        <v>-0.5354556912046665</v>
       </c>
       <c r="J11" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="K11" t="n">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3351563233443909</v>
+        <v>0.3324989546510689</v>
       </c>
       <c r="M11" t="n">
-        <v>4.716972344579726</v>
+        <v>4.718725583519769</v>
       </c>
       <c r="N11" t="n">
-        <v>33.75532058140557</v>
+        <v>33.69995399503411</v>
       </c>
       <c r="O11" t="n">
-        <v>5.80993292400227</v>
+        <v>5.805166147065397</v>
       </c>
       <c r="P11" t="n">
-        <v>356.8022104509805</v>
+        <v>356.7442189437267</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37624,7 +37842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L690"/>
+  <dimension ref="A1:L694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80393,7 +80611,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>-43.46144018180407,169.76236988503794</t>
+          <t>-43.46144217341612,169.76237756459386</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
@@ -80404,6 +80622,254 @@
       <c r="L690" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:19:37+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-43.465896874856355,169.7588206455483</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-43.46541744101441,169.75943857002588</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-43.46487220716396,169.75993165272433</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-43.46430922250207,169.76038722269453</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-43.46376596544239,169.7608813788471</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-43.4632054599317,169.7613363911382</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>-43.462642097738396,169.76173932658682</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>-43.462058212550666,169.76209377653768</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>-43.46144247517548,169.76237872816296</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>-43.460850358885736,169.7627621356683</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:25:50+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>-43.46588897883146,169.75880577261904</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>-43.465407796277304,169.7594204031547</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-43.464867375273826,169.75992242634248</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-43.464303774901985,169.76037647625623</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>-43.463760486080325,169.76087036251909</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>-43.46320183192066,169.7613287273919</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>-43.46263984581209,169.76173313919023</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>-43.46205654308483,169.76208777673193</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>-43.46144356150908,169.76238291701193</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>-43.460851228401516,169.76276564343496</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:25:58+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>-43.465887971955674,169.75880387607128</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>-43.465405464582204,169.75941601116477</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>-43.46486401395852,169.7599160079908</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-43.46430125667145,169.7603715085637</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>-43.463757137580785,169.76086363031965</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>-43.46320443036104,169.76133421629117</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>-43.462641695608724,169.76173822169454</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>-43.462059914121305,169.76209989172466</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>-43.46144645839794,169.76239408727653</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>-43.46085041685346,169.7627623695194</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>-43.465887071066774,169.7588021791602</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>-43.46540318588004,169.7594117189931</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-43.464861913136296,169.75991199652134</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-43.4642987384407,169.7603665408716</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>-43.46375500671724,169.76085934619314</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>-43.46320599923059,169.7613375303438</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>-43.46264551584022,169.76174871817184</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>-43.46206151937633,169.76210566076932</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>-43.461449717396654,169.7624066538256</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>-43.4608506777082,169.7627634218494</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L694"/>
+  <dimension ref="A1:L697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29596,6 +29596,132 @@
       <c r="L694" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="C695" t="n">
+        <v>353.61</v>
+      </c>
+      <c r="D695" t="n">
+        <v>354.03</v>
+      </c>
+      <c r="E695" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="F695" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="G695" t="n">
+        <v>358.21</v>
+      </c>
+      <c r="H695" t="n">
+        <v>361.66</v>
+      </c>
+      <c r="I695" t="n">
+        <v>355.93</v>
+      </c>
+      <c r="J695" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="K695" t="n">
+        <v>345.78</v>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:26:10+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="C696" t="n">
+        <v>352.75</v>
+      </c>
+      <c r="D696" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="E696" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="F696" t="n">
+        <v>356.59</v>
+      </c>
+      <c r="G696" t="n">
+        <v>356.81</v>
+      </c>
+      <c r="H696" t="n">
+        <v>360.03</v>
+      </c>
+      <c r="I696" t="n">
+        <v>353.89</v>
+      </c>
+      <c r="J696" t="n">
+        <v>353.1</v>
+      </c>
+      <c r="K696" t="n">
+        <v>344.32</v>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="C697" t="n">
+        <v>352.97</v>
+      </c>
+      <c r="D697" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="E697" t="n">
+        <v>355.71</v>
+      </c>
+      <c r="F697" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="G697" t="n">
+        <v>356.14</v>
+      </c>
+      <c r="H697" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="I697" t="n">
+        <v>353.73</v>
+      </c>
+      <c r="J697" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="K697" t="n">
+        <v>344.7</v>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29610,7 +29736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B730"/>
+  <dimension ref="A1:B733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36913,6 +37039,36 @@
       </c>
       <c r="B730" t="n">
         <v>1.02</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -37081,28 +37237,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5609820514873879</v>
+        <v>-0.5549836493768384</v>
       </c>
       <c r="J2" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K2" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2700061116535737</v>
+        <v>0.2667664673384643</v>
       </c>
       <c r="M2" t="n">
-        <v>5.571092359118984</v>
+        <v>5.573089861594251</v>
       </c>
       <c r="N2" t="n">
-        <v>49.8154578656691</v>
+        <v>49.82342367726333</v>
       </c>
       <c r="O2" t="n">
-        <v>7.058006649590881</v>
+        <v>7.058570937326006</v>
       </c>
       <c r="P2" t="n">
-        <v>371.4335229744342</v>
+        <v>371.3701242063925</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37159,28 +37315,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5108538757731814</v>
+        <v>-0.5023812775914196</v>
       </c>
       <c r="J3" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K3" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1938873349976354</v>
+        <v>0.1890937178647788</v>
       </c>
       <c r="M3" t="n">
-        <v>6.51142049232587</v>
+        <v>6.52904417625532</v>
       </c>
       <c r="N3" t="n">
-        <v>63.52727881984223</v>
+        <v>63.69752622547657</v>
       </c>
       <c r="O3" t="n">
-        <v>7.970400166857511</v>
+        <v>7.981072999633356</v>
       </c>
       <c r="P3" t="n">
-        <v>356.736255485636</v>
+        <v>356.6467050380413</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37237,28 +37393,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3748241911863279</v>
+        <v>-0.3655884410471955</v>
       </c>
       <c r="J4" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K4" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1231373622807498</v>
+        <v>0.1178961643504839</v>
       </c>
       <c r="M4" t="n">
-        <v>6.037061104265709</v>
+        <v>6.054663704863989</v>
       </c>
       <c r="N4" t="n">
-        <v>58.57570286900098</v>
+        <v>58.85279009567383</v>
       </c>
       <c r="O4" t="n">
-        <v>7.65347652175147</v>
+        <v>7.671557214521301</v>
       </c>
       <c r="P4" t="n">
-        <v>352.0170550784688</v>
+        <v>351.9194419480578</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37315,28 +37471,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2771289682466977</v>
+        <v>-0.2665044832444181</v>
       </c>
       <c r="J5" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K5" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06225274096955968</v>
+        <v>0.0577946479339646</v>
       </c>
       <c r="M5" t="n">
-        <v>6.451200659864848</v>
+        <v>6.471780200304297</v>
       </c>
       <c r="N5" t="n">
-        <v>67.73478231170694</v>
+        <v>68.14423070357427</v>
       </c>
       <c r="O5" t="n">
-        <v>8.230114355931327</v>
+        <v>8.254951889840077</v>
       </c>
       <c r="P5" t="n">
-        <v>351.6123480781402</v>
+        <v>351.5000580722283</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37393,28 +37549,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2661085033796872</v>
+        <v>-0.255890805829421</v>
       </c>
       <c r="J6" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K6" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04751842005635454</v>
+        <v>0.04416782478013082</v>
       </c>
       <c r="M6" t="n">
-        <v>7.453294858578125</v>
+        <v>7.46378423035013</v>
       </c>
       <c r="N6" t="n">
-        <v>83.10605411573476</v>
+        <v>83.39636249414028</v>
       </c>
       <c r="O6" t="n">
-        <v>9.116252196804055</v>
+        <v>9.132160888537843</v>
       </c>
       <c r="P6" t="n">
-        <v>351.5812186535825</v>
+        <v>351.4732277556146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37471,28 +37627,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.276742667557932</v>
+        <v>-0.2689750747089661</v>
       </c>
       <c r="J7" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K7" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05525383097355341</v>
+        <v>0.05258282579029416</v>
       </c>
       <c r="M7" t="n">
-        <v>7.069020548641264</v>
+        <v>7.07276954663815</v>
       </c>
       <c r="N7" t="n">
-        <v>76.67001613327801</v>
+        <v>76.71556987559798</v>
       </c>
       <c r="O7" t="n">
-        <v>8.756141623642117</v>
+        <v>8.758742482548392</v>
       </c>
       <c r="P7" t="n">
-        <v>355.1834916305806</v>
+        <v>355.1013970858174</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37549,28 +37705,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2736533168600668</v>
+        <v>-0.2650934709414598</v>
       </c>
       <c r="J8" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K8" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05587869422478065</v>
+        <v>0.05278377025145575</v>
       </c>
       <c r="M8" t="n">
-        <v>6.888626551561914</v>
+        <v>6.903401448538218</v>
       </c>
       <c r="N8" t="n">
-        <v>74.0804388733516</v>
+        <v>74.21794001249891</v>
       </c>
       <c r="O8" t="n">
-        <v>8.606999411720183</v>
+        <v>8.614983459792533</v>
       </c>
       <c r="P8" t="n">
-        <v>357.436162044028</v>
+        <v>357.3456943875631</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37627,28 +37783,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.318248919119416</v>
+        <v>-0.3104034722116398</v>
       </c>
       <c r="J9" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K9" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07881228502716109</v>
+        <v>0.07553673568318042</v>
       </c>
       <c r="M9" t="n">
-        <v>6.897047195723663</v>
+        <v>6.905837346742202</v>
       </c>
       <c r="N9" t="n">
-        <v>69.31203615049857</v>
+        <v>69.3979587948544</v>
       </c>
       <c r="O9" t="n">
-        <v>8.325385045179507</v>
+        <v>8.330543727443869</v>
       </c>
       <c r="P9" t="n">
-        <v>353.6803740224377</v>
+        <v>353.5974569149651</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37705,28 +37861,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.465457750455376</v>
+        <v>-0.4560388450500554</v>
       </c>
       <c r="J10" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K10" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2118493923962129</v>
+        <v>0.2047444303847692</v>
       </c>
       <c r="M10" t="n">
-        <v>5.48140954760987</v>
+        <v>5.506241788364277</v>
       </c>
       <c r="N10" t="n">
-        <v>47.19142468872106</v>
+        <v>47.54013461468291</v>
       </c>
       <c r="O10" t="n">
-        <v>6.869601494171336</v>
+        <v>6.894935432234512</v>
       </c>
       <c r="P10" t="n">
-        <v>354.8581520084099</v>
+        <v>354.7586039714827</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37783,28 +37939,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5354556912046665</v>
+        <v>-0.5332216716915793</v>
       </c>
       <c r="J11" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="K11" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3324989546510689</v>
+        <v>0.3325327532650618</v>
       </c>
       <c r="M11" t="n">
-        <v>4.718725583519769</v>
+        <v>4.709995109137019</v>
       </c>
       <c r="N11" t="n">
-        <v>33.69995399503411</v>
+        <v>33.58715553677818</v>
       </c>
       <c r="O11" t="n">
-        <v>5.805166147065397</v>
+        <v>5.795442652358677</v>
       </c>
       <c r="P11" t="n">
-        <v>356.7442189437267</v>
+        <v>356.720609196401</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37842,7 +37998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L694"/>
+  <dimension ref="A1:L697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80873,6 +81029,192 @@
         </is>
       </c>
     </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>-43.46588161273947,169.7587918978765</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>-43.46539926439221,169.7594043324659</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>-43.46486086272513,169.75990999078675</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-43.46429992046738,169.7603688726454</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>-43.46375409348997,169.760857510139</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>-43.46320658755665,169.76133877311358</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>-43.462642741145864,169.7617410944145</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>-43.46206116622025,169.76210439157947</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>-43.4614494759894,169.76240572297007</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>-43.460854677479716,169.76277955757698</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:26:10+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>-43.4658836264914,169.75879569097125</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>-43.46540382179694,169.7594129168084</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-43.464867480314915,169.759922626916</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-43.46430531667569,169.7603795177008</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>-43.46376038461065,169.76087015851306</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>-43.46321345135971,169.76135327209613</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>-43.46264929585785,169.76175910416126</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>-43.46206771565812,169.7621279292847</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>-43.46145505853053,169.7624272490063</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>-43.46085890911963,169.7627966287115</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>-43.46588553425627,169.75879928442967</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>-43.46540265594928,169.7594107208137</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>-43.464870473986046,169.7599283432611</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-43.4643118949093,169.7603924945329</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-43.46376515368511,169.76087974679837</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>-43.46321673617914,169.7613602108961</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>-43.462652070551066,169.76176672792033</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>-43.46206822933932,169.76212977537946</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>-43.46145608451064,169.76243120514312</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>-43.46085780773414,169.76279218553927</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
